--- a/data/file_generation/input/data_219/訂單明細_20251210-20251210.xlsx
+++ b/data/file_generation/input/data_219/訂單明細_20251210-20251210.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvchengguang\Documents\WXWork\1688854076421011\Cache\File\2026-02\lvcg\input\data_219\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenguanzhou/Downloads/标注0206-lvcg/澳鹏-数值统计数据编辑/input/data_219/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA77DA9-34B5-43D3-9D98-D37187F75228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E51FE54-9524-E84B-989F-E4ACA2506B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="訂單明細_20251210-20251210" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="123">
   <si>
     <t>訂單編號</t>
   </si>
@@ -71,9 +71,6 @@
     <t>2510165935013</t>
   </si>
   <si>
-    <t>来一桶香辣牛肉桶面</t>
-  </si>
-  <si>
     <t>ALICN支付</t>
   </si>
   <si>
@@ -83,93 +80,60 @@
     <t>2510168366643</t>
   </si>
   <si>
-    <t>卤蛋</t>
-  </si>
-  <si>
     <t>202512101100415367</t>
   </si>
   <si>
     <t>2511279606933</t>
   </si>
   <si>
-    <t>星选咖啡拿铁咖啡饮料</t>
-  </si>
-  <si>
     <t>202512101105596951</t>
   </si>
   <si>
     <t>2511258740667</t>
   </si>
   <si>
-    <t>零度无糖可乐摩登罐</t>
-  </si>
-  <si>
     <t>202512101116109491</t>
   </si>
   <si>
     <t>2511251593195</t>
   </si>
   <si>
-    <t>香脆面奥尔良鸡翅味</t>
-  </si>
-  <si>
     <t>202512101127366132</t>
   </si>
   <si>
     <t>2511253341811</t>
   </si>
   <si>
-    <t>夹心饼干原味</t>
-  </si>
-  <si>
     <t>202512101130306774</t>
   </si>
   <si>
     <t>2511278968374</t>
   </si>
   <si>
-    <t>牧场吐司</t>
-  </si>
-  <si>
     <t>202512101302531182</t>
   </si>
   <si>
     <t>2510163025364</t>
   </si>
   <si>
-    <t>青柠味维生素饮料</t>
-  </si>
-  <si>
     <t>202512101323589334</t>
   </si>
   <si>
     <t>2511275819275</t>
   </si>
   <si>
-    <t>茉莉乌龙无糖</t>
-  </si>
-  <si>
     <t>2511259078158</t>
   </si>
   <si>
-    <t>百岁山矿泉水</t>
-  </si>
-  <si>
     <t>202512101329035261</t>
   </si>
   <si>
     <t>2511273845118</t>
   </si>
   <si>
-    <t>美汁源果粒橙</t>
-  </si>
-  <si>
     <t>2511274113697</t>
   </si>
   <si>
-    <t>冰红茶饮料</t>
-  </si>
-  <si>
     <t>202512101333222277</t>
   </si>
   <si>
@@ -179,18 +143,12 @@
     <t>2511271883711</t>
   </si>
   <si>
-    <t>果滋果心青葡萄味</t>
-  </si>
-  <si>
     <t>202512101403095985</t>
   </si>
   <si>
     <t>2510158003540</t>
   </si>
   <si>
-    <t>水特运动饮料</t>
-  </si>
-  <si>
     <t>202512101403558865</t>
   </si>
   <si>
@@ -200,9 +158,6 @@
     <t>2511271336852</t>
   </si>
   <si>
-    <t>维生素功能饮料</t>
-  </si>
-  <si>
     <t>202512101431052186</t>
   </si>
   <si>
@@ -218,9 +173,6 @@
     <t>2511270903297</t>
   </si>
   <si>
-    <t>维生素风味饮料</t>
-  </si>
-  <si>
     <t>202512101616461191</t>
   </si>
   <si>
@@ -230,9 +182,6 @@
     <t>2510153068379</t>
   </si>
   <si>
-    <t>茉莉蜜茶</t>
-  </si>
-  <si>
     <t>202512101633132494</t>
   </si>
   <si>
@@ -272,9 +221,6 @@
     <t>2511270697501</t>
   </si>
   <si>
-    <t>干脆面烧烤鸡肉味</t>
-  </si>
-  <si>
     <t>202512102032388522</t>
   </si>
   <si>
@@ -291,13 +237,179 @@
   </si>
   <si>
     <t>202512102222488512</t>
+  </si>
+  <si>
+    <t>商品1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品2</t>
+  </si>
+  <si>
+    <t>商品3</t>
+  </si>
+  <si>
+    <t>商品4</t>
+  </si>
+  <si>
+    <t>商品5</t>
+  </si>
+  <si>
+    <t>商品6</t>
+  </si>
+  <si>
+    <t>商品7</t>
+  </si>
+  <si>
+    <t>商品8</t>
+  </si>
+  <si>
+    <t>商品9</t>
+  </si>
+  <si>
+    <t>商品10</t>
+  </si>
+  <si>
+    <t>商品11</t>
+  </si>
+  <si>
+    <t>商品12</t>
+  </si>
+  <si>
+    <t>商品13</t>
+  </si>
+  <si>
+    <t>商品14</t>
+  </si>
+  <si>
+    <t>商品15</t>
+  </si>
+  <si>
+    <t>商品16</t>
+  </si>
+  <si>
+    <t>商品17</t>
+  </si>
+  <si>
+    <t>商品18</t>
+  </si>
+  <si>
+    <t>商品19</t>
+  </si>
+  <si>
+    <t>商品20</t>
+  </si>
+  <si>
+    <t>商品21</t>
+  </si>
+  <si>
+    <t>商品22</t>
+  </si>
+  <si>
+    <t>商品23</t>
+  </si>
+  <si>
+    <t>商品24</t>
+  </si>
+  <si>
+    <t>商品25</t>
+  </si>
+  <si>
+    <t>商品26</t>
+  </si>
+  <si>
+    <t>商品27</t>
+  </si>
+  <si>
+    <t>商品28</t>
+  </si>
+  <si>
+    <t>商品29</t>
+  </si>
+  <si>
+    <t>商品30</t>
+  </si>
+  <si>
+    <t>商品31</t>
+  </si>
+  <si>
+    <t>商品32</t>
+  </si>
+  <si>
+    <t>商品33</t>
+  </si>
+  <si>
+    <t>商品34</t>
+  </si>
+  <si>
+    <t>商品35</t>
+  </si>
+  <si>
+    <t>商品36</t>
+  </si>
+  <si>
+    <t>商品37</t>
+  </si>
+  <si>
+    <t>商品38</t>
+  </si>
+  <si>
+    <t>商品39</t>
+  </si>
+  <si>
+    <t>商品40</t>
+  </si>
+  <si>
+    <t>商品41</t>
+  </si>
+  <si>
+    <t>商品42</t>
+  </si>
+  <si>
+    <t>商品43</t>
+  </si>
+  <si>
+    <t>商品44</t>
+  </si>
+  <si>
+    <t>商品45</t>
+  </si>
+  <si>
+    <t>商品46</t>
+  </si>
+  <si>
+    <t>商品47</t>
+  </si>
+  <si>
+    <t>商品48</t>
+  </si>
+  <si>
+    <t>商品49</t>
+  </si>
+  <si>
+    <t>商品50</t>
+  </si>
+  <si>
+    <t>商品51</t>
+  </si>
+  <si>
+    <t>商品52</t>
+  </si>
+  <si>
+    <t>商品53</t>
+  </si>
+  <si>
+    <t>商品54</t>
+  </si>
+  <si>
+    <t>商品55</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,6 +420,15 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -334,7 +455,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -342,6 +463,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -833,19 +957,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I56"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20.375" customWidth="1"/>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="3" width="14.875" customWidth="1"/>
-    <col min="4" max="4" width="21.25" customWidth="1"/>
-    <col min="5" max="5" width="8.875" customWidth="1"/>
-    <col min="6" max="6" width="10.875" customWidth="1"/>
-    <col min="7" max="7" width="8.875" customWidth="1"/>
-    <col min="8" max="9" width="18.25" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.1640625" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.1640625" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="8" max="9" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -874,7 +998,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -884,17 +1008,17 @@
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
-        <v>12</v>
+      <c r="D2" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1">
         <v>46001.370555555601</v>
@@ -903,7 +1027,7 @@
         <v>46001.370902777802</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -911,19 +1035,19 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1">
         <v>46001.370555555601</v>
@@ -932,27 +1056,27 @@
         <v>46001.370902777802</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4" s="1">
         <v>46001.417152777802</v>
@@ -961,27 +1085,27 @@
         <v>46001.417407407404</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="1">
         <v>46001.420844907399</v>
@@ -990,27 +1114,27 @@
         <v>46001.4211111111</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="1">
         <v>46001.427916666697</v>
@@ -1019,27 +1143,27 @@
         <v>46001.4281134259</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" s="1">
         <v>46001.435844907399</v>
@@ -1048,27 +1172,27 @@
         <v>46001.4385763889</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" s="1">
         <v>46001.435844907399</v>
@@ -1077,27 +1201,27 @@
         <v>46001.4385763889</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H9" s="1">
         <v>46001.437870370399</v>
@@ -1106,27 +1230,27 @@
         <v>46001.438148148103</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H10" s="1">
         <v>46001.437870370399</v>
@@ -1135,27 +1259,27 @@
         <v>46001.438148148103</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" s="1">
         <v>46001.502025463</v>
@@ -1164,27 +1288,27 @@
         <v>46001.5024305556</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H12" s="1">
         <v>46001.516655092601</v>
@@ -1193,27 +1317,27 @@
         <v>46001.516898148097</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H13" s="1">
         <v>46001.516655092601</v>
@@ -1222,27 +1346,27 @@
         <v>46001.516898148097</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
+        <v>31</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H14" s="1">
         <v>46001.520196759302</v>
@@ -1251,27 +1375,27 @@
         <v>46001.520879629599</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
+        <v>32</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H15" s="1">
         <v>46001.520196759302</v>
@@ -1280,9 +1404,9 @@
         <v>46001.520879629599</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -1290,17 +1414,17 @@
       <c r="C16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D16" t="s">
-        <v>12</v>
+      <c r="D16" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H16" s="1">
         <v>46001.520196759302</v>
@@ -1309,27 +1433,27 @@
         <v>46001.520879629599</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17" s="1">
         <v>46001.523182870398</v>
@@ -1338,27 +1462,27 @@
         <v>46001.523692129602</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="1">
         <v>46001.523182870398</v>
@@ -1367,9 +1491,9 @@
         <v>46001.523692129602</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -1377,17 +1501,17 @@
       <c r="C19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D19" t="s">
-        <v>12</v>
+      <c r="D19" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H19" s="1">
         <v>46001.523182870398</v>
@@ -1396,27 +1520,27 @@
         <v>46001.523692129602</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" t="s">
-        <v>48</v>
+        <v>35</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="1">
         <v>46001.525462963</v>
@@ -1425,27 +1549,27 @@
         <v>46001.526990740698</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="E21">
         <v>2</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H21" s="1">
         <v>46001.525462963</v>
@@ -1454,27 +1578,27 @@
         <v>46001.526990740698</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" t="s">
-        <v>51</v>
+        <v>37</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H22" s="1">
         <v>46001.543877314798</v>
@@ -1483,27 +1607,27 @@
         <v>46001.5441319444</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" t="s">
-        <v>51</v>
+        <v>37</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H23" s="1">
         <v>46001.544409722199</v>
@@ -1512,27 +1636,27 @@
         <v>46001.544664351903</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H24" s="1">
         <v>46001.545173611099</v>
@@ -1541,27 +1665,27 @@
         <v>46001.546620370398</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E25">
         <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H25" s="1">
         <v>46001.5632638889</v>
@@ -1570,27 +1694,27 @@
         <v>46001.563587962999</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" s="1">
         <v>46001.5715277778</v>
@@ -1599,27 +1723,27 @@
         <v>46001.571782407402</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H27" s="1">
         <v>46001.630219907398</v>
@@ -1628,27 +1752,27 @@
         <v>46001.630914351903</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" t="s">
-        <v>48</v>
+        <v>35</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" s="1">
         <v>46001.630219907398</v>
@@ -1657,27 +1781,27 @@
         <v>46001.630914351903</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" t="s">
-        <v>42</v>
+        <v>31</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H29" s="1">
         <v>46001.630219907398</v>
@@ -1686,27 +1810,27 @@
         <v>46001.630914351903</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H30" s="1">
         <v>46001.634131944404</v>
@@ -1715,27 +1839,27 @@
         <v>46001.634548611102</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" t="s">
-        <v>61</v>
+        <v>45</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H31" s="1">
         <v>46001.634131944404</v>
@@ -1744,27 +1868,27 @@
         <v>46001.634548611102</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" t="s">
-        <v>48</v>
+        <v>35</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H32" s="1">
         <v>46001.634131944404</v>
@@ -1773,27 +1897,27 @@
         <v>46001.634548611102</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H33" s="1">
         <v>46001.634131944404</v>
@@ -1802,27 +1926,27 @@
         <v>46001.634548611102</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H34" s="1">
         <v>46001.636666666702</v>
@@ -1831,27 +1955,27 @@
         <v>46001.639293981498</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35" s="1">
         <v>46001.636666666702</v>
@@ -1860,27 +1984,27 @@
         <v>46001.639293981498</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H36" s="1">
         <v>46001.644351851799</v>
@@ -1889,27 +2013,27 @@
         <v>46001.644641203697</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" t="s">
-        <v>65</v>
+        <v>48</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H37" s="1">
         <v>46001.644351851799</v>
@@ -1918,27 +2042,27 @@
         <v>46001.644641203697</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" t="s">
-        <v>48</v>
+        <v>35</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="E38">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H38" s="1">
         <v>46001.6480787037</v>
@@ -1947,27 +2071,27 @@
         <v>46001.648321759298</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:9">
       <c r="A39" s="2" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H39" s="1">
         <v>46001.650335648097</v>
@@ -1976,27 +2100,27 @@
         <v>46001.650520833296</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H40" s="1">
         <v>46001.662916666697</v>
@@ -2005,27 +2129,27 @@
         <v>46001.663645833301</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:9">
       <c r="A41" s="2" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="E41">
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H41" s="1">
         <v>46001.663310185198</v>
@@ -2034,27 +2158,27 @@
         <v>46001.663483796299</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D42" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H42" s="1">
         <v>46001.663668981499</v>
@@ -2063,27 +2187,27 @@
         <v>46001.663877314801</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D43" t="s">
-        <v>61</v>
+        <v>45</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H43" s="1">
         <v>46001.664432870399</v>
@@ -2092,27 +2216,27 @@
         <v>46001.665601851899</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" t="s">
-        <v>65</v>
+        <v>48</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="E44">
         <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44" s="1">
         <v>46001.664814814802</v>
@@ -2121,27 +2245,27 @@
         <v>46001.664988425902</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" t="s">
-        <v>42</v>
+        <v>31</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H45" s="1">
         <v>46001.714074074102</v>
@@ -2150,27 +2274,27 @@
         <v>46001.714293981502</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H46" s="1">
         <v>46001.737222222197</v>
@@ -2179,27 +2303,27 @@
         <v>46001.737511574102</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D47" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H47" s="1">
         <v>46001.737557870401</v>
@@ -2208,27 +2332,27 @@
         <v>46001.737766203703</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H48" s="1">
         <v>46001.804513888899</v>
@@ -2237,27 +2361,27 @@
         <v>46001.804814814801</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D49" t="s">
-        <v>79</v>
+        <v>61</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="E49">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H49" s="1">
         <v>46001.804513888899</v>
@@ -2266,27 +2390,27 @@
         <v>46001.804814814801</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D50" t="s">
-        <v>65</v>
+        <v>48</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50" s="1">
         <v>46001.814351851899</v>
@@ -2295,27 +2419,27 @@
         <v>46001.814606481501</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9">
       <c r="A51" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H51" s="1">
         <v>46001.814953703702</v>
@@ -2324,27 +2448,27 @@
         <v>46001.815324074101</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D52" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H52" s="1">
         <v>46001.8679976852</v>
@@ -2353,27 +2477,27 @@
         <v>46001.8733333333</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9">
       <c r="A53" s="2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D53" t="s">
-        <v>79</v>
+        <v>61</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H53" s="1">
         <v>46001.8679976852</v>
@@ -2382,27 +2506,27 @@
         <v>46001.8733333333</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D54" t="s">
-        <v>31</v>
+        <v>24</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H54" s="1">
         <v>46001.888831018499</v>
@@ -2411,27 +2535,27 @@
         <v>46001.889016203699</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" t="s">
-        <v>61</v>
+        <v>45</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H55" s="1">
         <v>46001.889374999999</v>
@@ -2440,27 +2564,27 @@
         <v>46001.889537037001</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D56" t="s">
-        <v>28</v>
+        <v>22</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H56" s="1">
         <v>46001.890844907401</v>
@@ -2634,18 +2758,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E160D55-7FA4-42FA-9B63-4890B8EDB755}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9F8CEDC-4DEA-42F6-AA0C-B8C80D7F0956}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03B2A364-91E9-421B-8193-6988338D08E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95022C46-04E1-499B-BF0B-3B3DC3BE5681}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D6C2018-FE92-4791-B354-08A4A9089ED3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B32F8D4-BD47-4901-9471-590551A4B0E4}"/>
 </file>